--- a/task199/golden/nota_vigilancia_2026S2.xlsx
+++ b/task199/golden/nota_vigilancia_2026S2.xlsx
@@ -1256,10 +1256,10 @@
         <v>61</v>
       </c>
       <c r="B4" s="4">
-        <v>275.6</v>
+        <v>275.7</v>
       </c>
       <c r="C4" s="3">
-        <v>34444</v>
+        <v>34460</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1267,10 +1267,10 @@
         <v>62</v>
       </c>
       <c r="B5" s="4">
-        <v>378.3</v>
+        <v>378.6</v>
       </c>
       <c r="C5" s="3">
-        <v>8702</v>
+        <v>8708</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1278,10 +1278,10 @@
         <v>63</v>
       </c>
       <c r="B6" s="4">
-        <v>302.9</v>
+        <v>303.1</v>
       </c>
       <c r="C6" s="3">
-        <v>29379</v>
+        <v>29399</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1289,10 +1289,10 @@
         <v>64</v>
       </c>
       <c r="B7" s="4">
-        <v>289.5</v>
+        <v>289.7</v>
       </c>
       <c r="C7" s="3">
-        <v>16501</v>
+        <v>16514</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1300,10 +1300,10 @@
         <v>65</v>
       </c>
       <c r="B8" s="4">
-        <v>162.5</v>
+        <v>162.6</v>
       </c>
       <c r="C8" s="3">
-        <v>4388</v>
+        <v>4390</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1311,10 +1311,10 @@
         <v>66</v>
       </c>
       <c r="B9" s="4">
-        <v>330.9</v>
+        <v>331.1</v>
       </c>
       <c r="C9" s="3">
-        <v>66170</v>
+        <v>66216</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1322,10 +1322,10 @@
         <v>67</v>
       </c>
       <c r="B10" s="4">
-        <v>355.9</v>
+        <v>356.5</v>
       </c>
       <c r="C10" s="3">
-        <v>5695</v>
+        <v>5704</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1333,10 +1333,10 @@
         <v>68</v>
       </c>
       <c r="B11" s="4">
-        <v>275.1</v>
+        <v>275.2</v>
       </c>
       <c r="C11" s="3">
-        <v>61902</v>
+        <v>61921</v>
       </c>
     </row>
   </sheetData>

--- a/task199/golden/nota_vigilancia_2026S2.xlsx
+++ b/task199/golden/nota_vigilancia_2026S2.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="84">
   <si>
     <t>Nota de vigilancia semestral, 1 de abril al 30 de septiembre de 2026</t>
   </si>
@@ -123,6 +123,9 @@
     <t>Facturado</t>
   </si>
   <si>
+    <t>Diferencia</t>
+  </si>
+  <si>
     <t>Valor facturado (miles COP)</t>
   </si>
   <si>
@@ -138,7 +141,13 @@
     <t>T4</t>
   </si>
   <si>
-    <t>Diferencias entre lo remitido en 2025 y lo facturado en 2025</t>
+    <t>Items que cierran la diferencia de cada trimestre</t>
+  </si>
+  <si>
+    <t>Remitido en</t>
+  </si>
+  <si>
+    <t>Facturado en</t>
   </si>
   <si>
     <t>Items</t>
@@ -147,7 +156,16 @@
     <t>Items publicados en diciembre de 2024 y remitidos en enero de 2025</t>
   </si>
   <si>
-    <t>Items publicados en diciembre de 2025 y remitidos en enero de 2026</t>
+    <t>no facturado</t>
+  </si>
+  <si>
+    <t>Items facturados en T1 y remitidos en T2</t>
+  </si>
+  <si>
+    <t>Items facturados en T2 y remitidos en T3</t>
+  </si>
+  <si>
+    <t>Items facturados en T3 y remitidos en T4</t>
   </si>
   <si>
     <t>Lote del 11 de agosto de 2025 rechazado y acreditado</t>
@@ -878,7 +896,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{775CF742-5179-5C4E-8422-FFDF2D2884DA}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="62.7109375" customWidth="1"/>
@@ -888,14 +906,15 @@
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="16.7109375" customWidth="1"/>
     <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>24</v>
       </c>
@@ -917,13 +936,16 @@
       <c r="G3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
         <v>3090</v>
@@ -940,16 +962,19 @@
       <c r="F4" s="3">
         <v>7351</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <v>7407</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="6">
+        <v>-56</v>
+      </c>
+      <c r="I4">
         <v>16545</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3">
         <v>3205</v>
@@ -966,16 +991,19 @@
       <c r="F5" s="3">
         <v>7599</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="3">
         <v>7531</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="6">
+        <v>68</v>
+      </c>
+      <c r="I5">
         <v>16812.7</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3">
         <v>3170</v>
@@ -992,16 +1020,19 @@
       <c r="F6" s="3">
         <v>7549</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="3">
         <v>7598</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="6">
+        <v>-49</v>
+      </c>
+      <c r="I6">
         <v>16980.5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="3">
         <v>3162</v>
@@ -1018,42 +1049,97 @@
       <c r="F7" s="3">
         <v>7360</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="3">
         <v>7234</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="6">
+        <v>126</v>
+      </c>
+      <c r="I7">
         <v>16174</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
         <v>36</v>
       </c>
-      <c r="B9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12">
+      <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="3">
         <v>7</v>
       </c>
     </row>
@@ -1074,23 +1160,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B4" s="3">
         <v>146</v>
@@ -1101,7 +1187,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B5" s="3">
         <v>17</v>
@@ -1112,7 +1198,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B6" s="3">
         <v>37</v>
@@ -1123,7 +1209,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B7" s="3">
         <v>131</v>
@@ -1134,7 +1220,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B8" s="3">
         <v>120</v>
@@ -1145,7 +1231,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B9" s="3">
         <v>58</v>
@@ -1156,7 +1242,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B10" s="3">
         <v>29</v>
@@ -1167,7 +1253,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B11" s="3">
         <v>56</v>
@@ -1178,7 +1264,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B12" s="3">
         <v>27</v>
@@ -1189,7 +1275,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B13" s="3">
         <v>66</v>
@@ -1200,7 +1286,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B14" s="3">
         <v>54</v>
@@ -1211,7 +1297,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B15" s="3">
         <v>89</v>
@@ -1237,23 +1323,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B4" s="4">
         <v>275.7</v>
@@ -1264,7 +1350,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B5" s="4">
         <v>378.6</v>
@@ -1275,7 +1361,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B6" s="4">
         <v>303.1</v>
@@ -1286,7 +1372,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B7" s="4">
         <v>289.7</v>
@@ -1297,7 +1383,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B8" s="4">
         <v>162.6</v>
@@ -1308,7 +1394,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B9" s="4">
         <v>331.1</v>
@@ -1319,24 +1405,24 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B10" s="4">
-        <v>356.5</v>
+        <v>356.2</v>
       </c>
       <c r="C10" s="3">
-        <v>5704</v>
+        <v>5699</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B11" s="4">
         <v>275.2</v>
       </c>
       <c r="C11" s="3">
-        <v>61921</v>
+        <v>61922</v>
       </c>
     </row>
   </sheetData>
@@ -1354,47 +1440,47 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
